--- a/whitelist_log.xlsx
+++ b/whitelist_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>67.36.18.24/32</t>
@@ -491,6 +490,118 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>dev and support</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>67.36.17.14/32</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-07-24 10:36:35</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>devloper5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>xtranet</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>dev and support</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>67.36.17.14/32</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-07-24 11:36:07</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>devloper5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>xtranet</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>dev and support</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>203.101.126.72/32</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2025-07-24 11:36:44</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>zafar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xtranet</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>dev and support</t>
         </is>

--- a/whitelist_log.xlsx
+++ b/whitelist_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,7 +580,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>203.101.126.72/32</t>
@@ -602,6 +601,81 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>dev and support</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>203.101.126.72/32</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-07-24 11:48:21</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>zafar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>xtranet</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>dev and support</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>203.101.129.72/32</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-07-24 11:48:47</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>zafar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>xtranet</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>dev and support</t>
         </is>

--- a/whitelist_log.xlsx
+++ b/whitelist_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,7 +654,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>203.101.129.72/32</t>
@@ -676,6 +675,44 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>dev and support</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>203.101.121.62/32</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-07-24 12:08:18</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>zafar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>xtranet</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>dev and support</t>
         </is>
